--- a/data/trans_orig/IP07A08-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A08-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30757</t>
+          <t>30617</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>20156</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29852</t>
+          <t>29950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42032</t>
+          <t>41431</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56909</t>
+          <t>57290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16507</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>27790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29699</t>
+          <t>30257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45035</t>
+          <t>45762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>21018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29379</t>
+          <t>29668</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42553</t>
+          <t>42408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>18107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30760</t>
+          <t>30443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>18967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30763</t>
+          <t>30438</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>32638</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48176</t>
+          <t>47262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>53,99%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18344</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29895</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33171</t>
+          <t>33348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47943</t>
+          <t>47882</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37854</t>
+          <t>38091</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52903</t>
+          <t>53074</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44849</t>
+          <t>45195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60356</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87589</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108877</t>
+          <t>108740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,62%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31223</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46208</t>
+          <t>46009</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42324</t>
+          <t>42216</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>62720</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83396</t>
+          <t>84111</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>23397</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>35336</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>34923</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47715</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61581</t>
+          <t>62777</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>79297</t>
+          <t>79744</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>25487</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20595</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>32667</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37285</t>
+          <t>37356</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54714</t>
+          <t>54287</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25987</t>
+          <t>25542</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>11624</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29540</t>
+          <t>29686</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>43842</t>
+          <t>43629</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,19%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23489</t>
+          <t>24186</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21843</t>
+          <t>22596</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>29086</t>
+          <t>28903</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>43775</t>
+          <t>42620</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,47 +4383,47 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>14,49%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>15,7%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>5415</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>140690</t>
+          <t>139050</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>167759</t>
+          <t>169158</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>161767</t>
+          <t>164810</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>192202</t>
+          <t>193157</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>309570</t>
+          <t>312582</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>349528</t>
+          <t>353087</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,71%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>111764</t>
+          <t>111832</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>138964</t>
+          <t>140628</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>116158</t>
+          <t>116553</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>145743</t>
+          <t>143906</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>238608</t>
+          <t>236582</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>277112</t>
+          <t>276715</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>22823</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>38309</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15353</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>26052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17280</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26511</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35368</t>
+          <t>36570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49798</t>
+          <t>50199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23070</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>16948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>22274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36656</t>
+          <t>35815</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,14%</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26391</t>
+          <t>26605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38278</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51438</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15337</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28197</t>
+          <t>28553</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27668</t>
+          <t>28098</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>33661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47843</t>
+          <t>47333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26278</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40677</t>
+          <t>39820</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45482</t>
+          <t>46574</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60810</t>
+          <t>61304</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46207</t>
+          <t>46621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62925</t>
+          <t>62033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97048</t>
+          <t>97699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119381</t>
+          <t>119485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,14%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37631</t>
+          <t>36908</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31654</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48846</t>
+          <t>48518</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58868</t>
+          <t>59024</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80421</t>
+          <t>79900</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>42703</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56271</t>
+          <t>56744</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>31402</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>44760</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78530</t>
+          <t>78454</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>97479</t>
+          <t>97537</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,84%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18850</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>31827</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23177</t>
+          <t>23489</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37419</t>
+          <t>37230</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45898</t>
+          <t>45372</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64203</t>
+          <t>65229</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>15434</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>24932</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24543</t>
+          <t>24339</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37578</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>58,88%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>20609</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>21975</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>34267</t>
+          <t>34264</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -9642,57 +9642,57 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
+          <t>3012</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
           <t>3092</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>167096</t>
+          <t>165927</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>195094</t>
+          <t>195363</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>161216</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>189487</t>
+          <t>189005</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>335930</t>
+          <t>337910</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>379750</t>
+          <t>378287</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>102135</t>
+          <t>101705</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>128956</t>
+          <t>130729</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>105598</t>
+          <t>106199</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>134612</t>
+          <t>134613</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>214163</t>
+          <t>215363</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>255932</t>
+          <t>255860</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>11783</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>25143</t>
+          <t>25828</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24455</t>
+          <t>24752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>31090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44501</t>
+          <t>44685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22371</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24621</t>
+          <t>25524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38833</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,31%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,47 +10989,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1752</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5481</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>28785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25547</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36103</t>
+          <t>37080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44759</t>
+          <t>45414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62053</t>
+          <t>62451</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,88%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21149</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>33913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21834</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35657</t>
+          <t>35242</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52100</t>
+          <t>52145</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>565</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17380</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27739</t>
+          <t>27163</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43146</t>
+          <t>43114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,39%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23156</t>
+          <t>24043</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>35463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58999</t>
+          <t>58742</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76497</t>
+          <t>75427</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48518</t>
+          <t>48951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65510</t>
+          <t>66100</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111764</t>
+          <t>111667</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136734</t>
+          <t>136217</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,3%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34158</t>
+          <t>34897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51999</t>
+          <t>51822</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32975</t>
+          <t>32859</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50281</t>
+          <t>50143</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72537</t>
+          <t>72895</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>97038</t>
+          <t>97402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14943</t>
+          <t>14343</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36397</t>
+          <t>36054</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50868</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33676</t>
+          <t>33635</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48161</t>
+          <t>48352</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74801</t>
+          <t>75728</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94816</t>
+          <t>96008</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>64,18%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34217</t>
+          <t>34379</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20932</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>34995</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45852</t>
+          <t>43636</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64151</t>
+          <t>63331</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11787</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27298</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31124</t>
+          <t>32262</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45522</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,65%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19380</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21040</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23608</t>
+          <t>23610</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>37273</t>
+          <t>37069</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>166336</t>
+          <t>166554</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>196277</t>
+          <t>198307</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>178205</t>
+          <t>177508</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>209110</t>
+          <t>208215</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>354311</t>
+          <t>353340</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>397920</t>
+          <t>396972</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>121953</t>
+          <t>122054</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>151444</t>
+          <t>150619</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>120110</t>
+          <t>120935</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>151032</t>
+          <t>150668</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>251890</t>
+          <t>250723</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>292661</t>
+          <t>294269</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,15%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>18939</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>38184</t>
+          <t>37798</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
